--- a/Unit_Test_Plan_v0.1 (1).xlsx
+++ b/Unit_Test_Plan_v0.1 (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LOQ\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03bb5f1981b8452f/Desktop/ai-resume-screening-engine/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E81821C-E5AE-4558-9B12-ED01A17F0038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{4E81821C-E5AE-4558-9B12-ED01A17F0038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBE5B0A7-8F4E-464D-B17E-C00585FD586D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>Actual Result</t>
   </si>
@@ -94,24 +94,102 @@
   </si>
   <si>
     <t>Workflow executed successfully</t>
+  </si>
+  <si>
+    <t>Ensuring Enterprise Tool works</t>
+  </si>
+  <si>
+    <t>Provide a valid job role to the Job Requirements Tool</t>
+  </si>
+  <si>
+    <t>Supported job role is provided</t>
+  </si>
+  <si>
+    <t>Required skills and experience should be returned</t>
+  </si>
+  <si>
+    <t>Job requirements returned successfully</t>
+  </si>
+  <si>
+    <t>Ensuring Tool Selection works</t>
+  </si>
+  <si>
+    <t>Send a request related to job requirements</t>
+  </si>
+  <si>
+    <t>Request requires job information</t>
+  </si>
+  <si>
+    <t>Appropriate enterprise tool should be selected and executed</t>
+  </si>
+  <si>
+    <t>Tool selected and executed successfully</t>
+  </si>
+  <si>
+    <t>Ensuring Job Agent works</t>
+  </si>
+  <si>
+    <t>Run the Job Agent with a valid job role</t>
+  </si>
+  <si>
+    <t>Valid job role is provided</t>
+  </si>
+  <si>
+    <t>Job requirements should be retrieved</t>
+  </si>
+  <si>
+    <t>Job information returned successfully</t>
+  </si>
+  <si>
+    <t>Ensuring Error Handling works</t>
+  </si>
+  <si>
+    <t>Provide an unsupported job role</t>
+  </si>
+  <si>
+    <t>Job role is not available</t>
+  </si>
+  <si>
+    <t>Appropriate error message should be returned</t>
+  </si>
+  <si>
+    <r>
+      <t>Job role not found</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> returned</t>
+    </r>
+  </si>
+  <si>
+    <t>Ensuring Milestone 2 Workflow Integration works</t>
+  </si>
+  <si>
+    <t>Run the complete workflow with resume and job role</t>
+  </si>
+  <si>
+    <t>Valid resume and job role are provided</t>
+  </si>
+  <si>
+    <t>Resume analysis, job requirements and feedback should be generated</t>
+  </si>
+  <si>
+    <t>Complete workflow executed successfully</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -126,6 +204,10 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -171,16 +253,16 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,8 +579,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
@@ -507,101 +589,193 @@
     <col min="6" max="6" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="31.2">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row r="2" spans="1:6">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="52.8">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row r="4" spans="1:6" ht="39.6">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+    <row r="5" spans="1:6" ht="52.8">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+    <row r="6" spans="1:6" ht="66">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="52.8">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="39.6">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="39.6">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="66">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
